--- a/artfynd/A 43019-2021 artfynd.xlsx
+++ b/artfynd/A 43019-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43019-2021 artfynd.xlsx
+++ b/artfynd/A 43019-2021 artfynd.xlsx
@@ -2738,10 +2738,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117675729</v>
+        <v>117675725</v>
       </c>
       <c r="B20" t="n">
-        <v>78514</v>
+        <v>57287</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2754,21 +2754,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2778,10 +2778,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>381394</v>
+        <v>381497</v>
       </c>
       <c r="R20" t="n">
-        <v>6705939</v>
+        <v>6705618</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3045,10 +3045,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117675725</v>
+        <v>117675729</v>
       </c>
       <c r="B23" t="n">
-        <v>57287</v>
+        <v>78514</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3061,21 +3061,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3085,10 +3085,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>381497</v>
+        <v>381394</v>
       </c>
       <c r="R23" t="n">
-        <v>6705618</v>
+        <v>6705939</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 43019-2021 artfynd.xlsx
+++ b/artfynd/A 43019-2021 artfynd.xlsx
@@ -2738,10 +2738,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117675725</v>
+        <v>117675722</v>
       </c>
       <c r="B20" t="n">
-        <v>57287</v>
+        <v>79592</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2750,25 +2750,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2778,10 +2778,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>381497</v>
+        <v>381519</v>
       </c>
       <c r="R20" t="n">
-        <v>6705618</v>
+        <v>6705920</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2822,6 +2822,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2843,7 +2844,7 @@
         <v>117675724</v>
       </c>
       <c r="B21" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2942,10 +2943,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117675722</v>
+        <v>117675725</v>
       </c>
       <c r="B22" t="n">
-        <v>79590</v>
+        <v>57288</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2954,25 +2955,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2982,10 +2983,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>381519</v>
+        <v>381497</v>
       </c>
       <c r="R22" t="n">
-        <v>6705920</v>
+        <v>6705618</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3026,7 +3027,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3048,7 +3048,7 @@
         <v>117675729</v>
       </c>
       <c r="B23" t="n">
-        <v>78514</v>
+        <v>78516</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
